--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -16422,7 +16422,7 @@
       </c>
       <c r="J6" s="185"/>
       <c r="K6" s="185">
-        <f>YEAR(L6)</f>
+        <f>YEAR(L6)-IF(MONTH(L6)&lt;4,1,0)</f>
         <v>2025</v>
       </c>
       <c r="L6" s="638">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="M6" s="639"/>
       <c r="N6" s="638">
-        <f>B32</f>
+        <f>MIN(IF(DATE(YEAR(L6),3,31)&gt;=L6,DATE(YEAR(L6),3,31),DATE(YEAR(L6)+1,3,31)),F21)</f>
         <v>46112</v>
       </c>
       <c r="O6" s="641"/>
@@ -16466,17 +16466,17 @@
       </c>
       <c r="J7" s="185"/>
       <c r="K7" s="185">
-        <f>YEAR(L7)</f>
+        <f>YEAR(L7)-IF(MONTH(L7)&lt;4,1,0)</f>
         <v>2026</v>
       </c>
       <c r="L7" s="638">
-        <f>B33</f>
+        <f>N6+1</f>
         <v>46113</v>
       </c>
       <c r="M7" s="639"/>
       <c r="N7" s="638">
-        <f>B56</f>
-        <v>46477</v>
+        <f>F21</f>
+        <v>46112</v>
       </c>
       <c r="O7" s="641"/>
       <c r="P7" s="310">
@@ -44974,8 +44974,8 @@
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="184">
-        <f>D34-C34+1</f>
-        <v>365</v>
+        <f>MAX(0,D34-C34+1)</f>
+        <v>0</v>
       </c>
       <c r="B34" s="182" t="s">
         <v>14</v>
@@ -45012,7 +45012,7 @@
     <row r="35" spans="1:12" s="40" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="184">
         <f>D34-C33+1</f>
-        <v>730</v>
+        <v>365</v>
       </c>
       <c r="B35" s="157"/>
       <c r="C35" s="420" t="s">

--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -16505,15 +16505,23 @@
         <v>18</v>
       </c>
       <c r="H8" s="253"/>
-      <c r="I8" s="253"/>
+      <c r="I8" s="185" t="inlineStr">
+        <is>
+          <t>Corporation Tax main rate</t>
+        </is>
+      </c>
       <c r="J8" s="253"/>
       <c r="K8" s="253"/>
       <c r="L8" s="253"/>
       <c r="M8" s="253"/>
       <c r="N8" s="253"/>
       <c r="O8" s="253"/>
-      <c r="P8" s="255"/>
-      <c r="Q8" s="255"/>
+      <c r="P8" s="310">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="255" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="253"/>
@@ -16527,7 +16535,11 @@
       <c r="F9" s="253"/>
       <c r="G9" s="255"/>
       <c r="H9" s="253"/>
-      <c r="I9" s="253"/>
+      <c r="I9" s="185" t="inlineStr">
+        <is>
+          <t>Marginal relief fraction</t>
+        </is>
+      </c>
       <c r="J9" s="253"/>
       <c r="K9" s="253"/>
       <c r="L9" s="262" t="s">
@@ -16538,7 +16550,9 @@
         <v>521</v>
       </c>
       <c r="O9" s="263"/>
-      <c r="P9" s="264"/>
+      <c r="P9" s="262">
+        <v>0.015</v>
+      </c>
       <c r="Q9" s="255"/>
     </row>
     <row r="10" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16623,14 +16637,20 @@
       <c r="F12" s="253"/>
       <c r="G12" s="255"/>
       <c r="H12" s="253"/>
-      <c r="I12" s="253"/>
+      <c r="I12" s="185" t="inlineStr">
+        <is>
+          <t>Marginal relief lower limit</t>
+        </is>
+      </c>
       <c r="J12" s="253"/>
       <c r="K12" s="253"/>
       <c r="L12" s="253"/>
       <c r="M12" s="265"/>
       <c r="N12" s="255"/>
       <c r="O12" s="253"/>
-      <c r="P12" s="255"/>
+      <c r="P12" s="262">
+        <v>50000</v>
+      </c>
       <c r="Q12" s="255"/>
     </row>
     <row r="13" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16649,14 +16669,20 @@
         <v>268</v>
       </c>
       <c r="H13" s="253"/>
-      <c r="I13" s="253"/>
+      <c r="I13" s="185" t="inlineStr">
+        <is>
+          <t>Marginal relief upper limit</t>
+        </is>
+      </c>
       <c r="J13" s="253"/>
       <c r="K13" s="253"/>
       <c r="L13" s="253"/>
       <c r="M13" s="253"/>
       <c r="N13" s="253"/>
       <c r="O13" s="253"/>
-      <c r="P13" s="253"/>
+      <c r="P13" s="262">
+        <v>250000</v>
+      </c>
       <c r="Q13" s="253"/>
     </row>
     <row r="14" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -44960,17 +44986,23 @@
         <v>0</v>
       </c>
       <c r="G33" s="441">
-        <f>Admin!P6</f>
+        <f>IF(F33&lt;=Admin!$P$12*A33/A35,Admin!P6,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H33" s="442"/>
       <c r="I33" s="187">
+        <f>J33-L33</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="167">
         <f>F33*G33/100</f>
         <v>0</v>
       </c>
-      <c r="J33" s="167"/>
       <c r="K33" s="161"/>
-      <c r="L33" s="38"/>
+      <c r="L33" s="38">
+        <f>IF(AND(F33&gt;Admin!$P$12*A33/A35,F33&lt;Admin!$P$13*A33/A35),(Admin!$P$13*A33/A35-F33)*Admin!$P$9,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="184">
@@ -44997,17 +45029,23 @@
         <v>0</v>
       </c>
       <c r="G34" s="441">
-        <f>Admin!P7</f>
+        <f>IF(F34&lt;=Admin!$P$12*A34/A35,Admin!P7,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H34" s="442"/>
       <c r="I34" s="187">
+        <f>J34-L34</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="167">
         <f>F34*G34/100</f>
         <v>0</v>
       </c>
-      <c r="J34" s="167"/>
       <c r="K34" s="161"/>
-      <c r="L34" s="38"/>
+      <c r="L34" s="38">
+        <f>IF(AND(F34&gt;Admin!$P$12*A34/A35,F34&lt;Admin!$P$13*A34/A35),(Admin!$P$13*A34/A35-F34)*Admin!$P$9,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:12" s="40" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="184">

--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -52816,7 +52816,7 @@
         <v>150</v>
       </c>
       <c r="AJ126" s="535">
-        <f>CorporationTax!I33</f>
+        <f>CorporationTax!J33</f>
         <v>0</v>
       </c>
       <c r="AK126" s="535"/>
@@ -52881,12 +52881,15 @@
       <c r="B128" s="209">
         <v>53</v>
       </c>
-      <c r="C128" s="483"/>
-      <c r="D128" s="483"/>
-      <c r="E128" s="483"/>
-      <c r="F128" s="483"/>
-      <c r="G128" s="483"/>
-      <c r="H128" s="483"/>
+      <c r="C128" s="545" t="str">
+        <f>IF(CorporationTax!A34&gt;0,CorporationTax!E34," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="D128" s="546"/>
+      <c r="E128" s="546"/>
+      <c r="F128" s="546"/>
+      <c r="G128" s="546"/>
+      <c r="H128" s="547"/>
       <c r="I128" s="198"/>
       <c r="J128" s="198"/>
       <c r="K128" s="198"/>
@@ -52896,13 +52899,16 @@
       <c r="M128" s="210" t="s">
         <v>150</v>
       </c>
-      <c r="N128" s="483"/>
-      <c r="O128" s="483"/>
-      <c r="P128" s="483"/>
-      <c r="Q128" s="483"/>
-      <c r="R128" s="483"/>
-      <c r="S128" s="483"/>
-      <c r="T128" s="483"/>
+      <c r="N128" s="522" t="str">
+        <f>IF(CorporationTax!A34&gt;0,CorporationTax!F34," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="O128" s="468"/>
+      <c r="P128" s="468"/>
+      <c r="Q128" s="468"/>
+      <c r="R128" s="468"/>
+      <c r="S128" s="468"/>
+      <c r="T128" s="534"/>
       <c r="U128" s="198"/>
       <c r="V128" s="198"/>
       <c r="W128" s="198"/>
@@ -52911,8 +52917,11 @@
         <v>55</v>
       </c>
       <c r="Z128" s="351"/>
-      <c r="AA128" s="483"/>
-      <c r="AB128" s="483"/>
+      <c r="AA128" s="548" t="str">
+        <f>IF(CorporationTax!A34&gt;0,CorporationTax!G34," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AB128" s="549"/>
       <c r="AC128" s="198"/>
       <c r="AD128" s="198"/>
       <c r="AE128" s="198"/>
@@ -52924,13 +52933,16 @@
       <c r="AI128" s="212" t="s">
         <v>150</v>
       </c>
-      <c r="AJ128" s="535"/>
-      <c r="AK128" s="468"/>
-      <c r="AL128" s="468"/>
-      <c r="AM128" s="468"/>
-      <c r="AN128" s="468"/>
-      <c r="AO128" s="468"/>
-      <c r="AP128" s="468"/>
+      <c r="AJ128" s="535">
+        <f>CorporationTax!J34</f>
+        <v>0</v>
+      </c>
+      <c r="AK128" s="535"/>
+      <c r="AL128" s="535"/>
+      <c r="AM128" s="535"/>
+      <c r="AN128" s="535"/>
+      <c r="AO128" s="535"/>
+      <c r="AP128" s="535"/>
       <c r="AQ128" s="224" t="s">
         <v>391</v>
       </c>
@@ -53168,11 +53180,14 @@
         <v>150</v>
       </c>
       <c r="X133" s="225"/>
-      <c r="Y133" s="514"/>
-      <c r="Z133" s="514"/>
-      <c r="AA133" s="514"/>
-      <c r="AB133" s="514"/>
-      <c r="AC133" s="514"/>
+      <c r="Y133" s="535">
+        <f>CorporationTax!L33+CorporationTax!L34</f>
+        <v>0</v>
+      </c>
+      <c r="Z133" s="535"/>
+      <c r="AA133" s="535"/>
+      <c r="AB133" s="535"/>
+      <c r="AC133" s="535"/>
       <c r="AD133" s="225"/>
       <c r="AE133" s="224" t="s">
         <v>391</v>
@@ -53270,11 +53285,14 @@
         <v>150</v>
       </c>
       <c r="X135" s="225"/>
-      <c r="Y135" s="514"/>
-      <c r="Z135" s="514"/>
-      <c r="AA135" s="514"/>
-      <c r="AB135" s="514"/>
-      <c r="AC135" s="514"/>
+      <c r="Y135" s="535">
+        <f>AJ131-Y133</f>
+        <v>0</v>
+      </c>
+      <c r="Z135" s="535"/>
+      <c r="AA135" s="535"/>
+      <c r="AB135" s="535"/>
+      <c r="AC135" s="535"/>
       <c r="AD135" s="225"/>
       <c r="AE135" s="224" t="s">
         <v>391</v>
@@ -53369,7 +53387,7 @@
         <v>66</v>
       </c>
       <c r="W137" s="543" t="str">
-        <f>IF(AJ131&gt;0,AJ131*100/AJ110," ")</f>
+        <f>IF(Y135&gt;0,Y135*100/AJ110," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="X137" s="544"/>
@@ -53791,7 +53809,7 @@
         <v>150</v>
       </c>
       <c r="AJ145" s="535">
-        <f>AJ131</f>
+        <f>Y135</f>
         <v>0</v>
       </c>
       <c r="AK145" s="468"/>

--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -12979,7 +12979,7 @@
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="11">
-        <f>E15</f>
+        <f>IF(COUNT(E43:E47,E49:E76,E80:E85)=0,0,E15)</f>
         <v>0</v>
       </c>
       <c r="F48" s="3"/>

--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -16594,18 +16594,10 @@
         <v>45778</v>
       </c>
       <c r="C11" s="253"/>
-      <c r="D11" s="253" t="s">
-        <v>501</v>
-      </c>
-      <c r="E11" s="262">
-        <v>12000</v>
-      </c>
-      <c r="F11" s="253" t="s">
-        <v>502</v>
-      </c>
-      <c r="G11" s="262">
-        <v>3000</v>
-      </c>
+      <c r="D11" s="253"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="262"/>
       <c r="H11" s="253"/>
       <c r="I11" s="253"/>
       <c r="J11" s="253"/>

--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -55397,7 +55397,7 @@
         <v>150</v>
       </c>
       <c r="AA177" s="522" t="str">
-        <f>IF((CorporationTax!H15+CorporationTax!H17)&gt;0,CorporationTax!H15+CorporationTax!H17," ")</f>
+        <f>IF((CorporationTax!I15+CorporationTax!I17)&gt;0,CorporationTax!I15+CorporationTax!I17," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AB177" s="522"/>
@@ -55415,7 +55415,7 @@
         <v>150</v>
       </c>
       <c r="AL177" s="522" t="str">
-        <f>IF(CorporationTax!H18&lt;&gt;0,CorporationTax!H18," ")</f>
+        <f>IF(CorporationTax!I18&lt;&gt;0,CorporationTax!I18," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AM177" s="522"/>
@@ -55507,7 +55507,7 @@
         <v>150</v>
       </c>
       <c r="AA179" s="522" t="str">
-        <f>IF(CorporationTax!H16&gt;0,CorporationTax!H16," ")</f>
+        <f>IF(CorporationTax!I16&gt;0,CorporationTax!I16," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AB179" s="522"/>

--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="626">
   <si>
     <t>Depreciation</t>
   </si>
@@ -2159,6 +2159,12 @@
   </si>
   <si>
     <t>(Small profits rate)</t>
+  </si>
+  <si>
+    <t>Copyright (C) 2006-2026 DIY Accounting Limited</t>
+  </si>
+  <si>
+    <t>Licensed under the PolyForm Internal Use License 1.0.0 with an additional grant for accountants. Free to use, source available: https://spreadsheets.diyaccounting.co.uk</t>
   </si>
 </sst>
 </file>
@@ -11957,7 +11963,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="11" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="0.83203125" style="6" customWidth="1"/>
@@ -13448,6 +13454,16 @@
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
+    </row>
+    <row r="88">
+      <c r="B88" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="s">
+        <v>625</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="19">

--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -44994,7 +44994,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="441">
-        <f>IF(F33&lt;=Admin!$P$12*A33/A35,Admin!P6,Admin!$P$8)</f>
+        <f>IF(F33&lt;=Admin!$P$12*A33/A35/(1+Admin!$P$14),Admin!P6,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H33" s="442"/>
@@ -45008,7 +45008,7 @@
       </c>
       <c r="K33" s="161"/>
       <c r="L33" s="38">
-        <f>IF(AND(F33&gt;Admin!$P$12*A33/A35,F33&lt;Admin!$P$13*A33/A35),(Admin!$P$13*A33/A35-F33)*Admin!$P$9,0)</f>
+        <f>IF(AND(F33&gt;Admin!$P$12*A33/A35/(1+Admin!$P$14),F33&lt;Admin!$P$13*A33/A35/(1+Admin!$P$14)),(Admin!$P$13*A33/A35/(1+Admin!$P$14)-F33)*Admin!$P$9,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -45037,7 +45037,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="441">
-        <f>IF(F34&lt;=Admin!$P$12*A34/A35,Admin!P7,Admin!$P$8)</f>
+        <f>IF(F34&lt;=Admin!$P$12*A34/A35/(1+Admin!$P$14),Admin!P7,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H34" s="442"/>
@@ -45051,7 +45051,7 @@
       </c>
       <c r="K34" s="161"/>
       <c r="L34" s="38">
-        <f>IF(AND(F34&gt;Admin!$P$12*A34/A35,F34&lt;Admin!$P$13*A34/A35),(Admin!$P$13*A34/A35-F34)*Admin!$P$9,0)</f>
+        <f>IF(AND(F34&gt;Admin!$P$12*A34/A35/(1+Admin!$P$14),F34&lt;Admin!$P$13*A34/A35/(1+Admin!$P$14)),(Admin!$P$13*A34/A35/(1+Admin!$P$14)-F34)*Admin!$P$9,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -52397,7 +52397,10 @@
         <v>40</v>
       </c>
       <c r="X118" s="553"/>
-      <c r="Y118" s="560"/>
+      <c r="Y118" s="560">
+        <f>Admin!$P$14</f>
+        <v>0</v>
+      </c>
       <c r="Z118" s="561"/>
       <c r="AA118" s="562"/>
       <c r="AB118" s="198"/>
@@ -52495,7 +52498,10 @@
         <v>41</v>
       </c>
       <c r="X120" s="553"/>
-      <c r="Y120" s="560"/>
+      <c r="Y120" s="560" t="str">
+        <f>IF(CorporationTax!A34&gt;0,Admin!$P$14," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="Z120" s="561"/>
       <c r="AA120" s="562"/>
       <c r="AB120" s="198"/>

--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -12112,9 +12112,13 @@
       </c>
       <c r="M6" s="348"/>
       <c r="N6" s="170"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="O6" s="338" t="inlineStr">
+        <is>
+          <t>Franked investment income</t>
+        </is>
+      </c>
+      <c r="P6" s="339"/>
+      <c r="Q6" s="11"/>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -13466,7 +13470,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="G10:K10"/>
     <mergeCell ref="E5:H5"/>
@@ -13485,6 +13489,7 @@
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
     <mergeCell ref="J6:K6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -44899,7 +44904,11 @@
     </row>
     <row r="29" spans="1:12" s="40" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A29" s="159"/>
-      <c r="B29" s="39"/>
+      <c r="B29" s="306" t="inlineStr">
+        <is>
+          <t>Add franked investment income (exempt distributions received)</t>
+        </is>
+      </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="157"/>
@@ -44908,12 +44917,19 @@
       <c r="H29" s="162"/>
       <c r="I29" s="161"/>
       <c r="J29" s="161"/>
-      <c r="K29" s="176"/>
+      <c r="K29" s="252">
+        <f>OpenAccounts!Q6</f>
+        <v>0</v>
+      </c>
       <c r="L29" s="39"/>
     </row>
     <row r="30" spans="1:12" s="40" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A30" s="158"/>
-      <c r="B30" s="39"/>
+      <c r="B30" s="306" t="inlineStr">
+        <is>
+          <t>Augmented profits, which the marginal relief limits are tested against</t>
+        </is>
+      </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="E30" s="177"/>
@@ -44922,7 +44938,10 @@
       <c r="H30" s="162"/>
       <c r="I30" s="161"/>
       <c r="J30" s="161"/>
-      <c r="K30" s="161"/>
+      <c r="K30" s="252">
+        <f>K28+K29</f>
+        <v>0</v>
+      </c>
       <c r="L30" s="39"/>
     </row>
     <row r="31" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -44994,7 +45013,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="441">
-        <f>IF(F33&lt;=Admin!$P$12*A33/A35/(1+Admin!$P$14),Admin!P6,Admin!$P$8)</f>
+        <f>IF(K30*A33/A35&lt;=Admin!$P$12*A33/A35/(1+Admin!$P$14),Admin!P6,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H33" s="442"/>
@@ -45008,7 +45027,7 @@
       </c>
       <c r="K33" s="161"/>
       <c r="L33" s="38">
-        <f>IF(AND(F33&gt;Admin!$P$12*A33/A35/(1+Admin!$P$14),F33&lt;Admin!$P$13*A33/A35/(1+Admin!$P$14)),(Admin!$P$13*A33/A35/(1+Admin!$P$14)-F33)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A33/A35&gt;Admin!$P$12*A33/A35/(1+Admin!$P$14),K30*A33/A35&lt;Admin!$P$13*A33/A35/(1+Admin!$P$14)),(Admin!$P$13*A33/A35/(1+Admin!$P$14)-K30*A33/A35)*F33/(K30*A33/A35)*Admin!$P$9,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -45037,7 +45056,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="441">
-        <f>IF(F34&lt;=Admin!$P$12*A34/A35/(1+Admin!$P$14),Admin!P7,Admin!$P$8)</f>
+        <f>IF(K30*A34/A35&lt;=Admin!$P$12*A34/A35/(1+Admin!$P$14),Admin!P7,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H34" s="442"/>
@@ -45051,7 +45070,7 @@
       </c>
       <c r="K34" s="161"/>
       <c r="L34" s="38">
-        <f>IF(AND(F34&gt;Admin!$P$12*A34/A35/(1+Admin!$P$14),F34&lt;Admin!$P$13*A34/A35/(1+Admin!$P$14)),(Admin!$P$13*A34/A35/(1+Admin!$P$14)-F34)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A34/A35&gt;Admin!$P$12*A34/A35/(1+Admin!$P$14),K30*A34/A35&lt;Admin!$P$13*A34/A35/(1+Admin!$P$14)),(Admin!$P$13*A34/A35/(1+Admin!$P$14)-K30*A34/A35)*F34/(K30*A34/A35)*Admin!$P$9,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -52198,7 +52217,10 @@
       <c r="Y114" s="210" t="s">
         <v>150</v>
       </c>
-      <c r="Z114" s="514"/>
+      <c r="Z114" s="514">
+        <f>CorporationTax!K29</f>
+        <v>0</v>
+      </c>
       <c r="AA114" s="514"/>
       <c r="AB114" s="514"/>
       <c r="AC114" s="514"/>

--- a/app/templates/ltd/Financialaccounts.xlsx
+++ b/app/templates/ltd/Financialaccounts.xlsx
@@ -16264,7 +16264,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.5" style="256" customWidth="1"/>
@@ -16388,7 +16388,7 @@
       <c r="P4" s="253"/>
       <c r="Q4" s="253"/>
     </row>
-    <row r="5" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="253"/>
       <c r="B5" s="330">
         <f>DATE(YEAR(B6),MONTH(B6),1)</f>
@@ -16418,8 +16418,28 @@
         <v>623</v>
       </c>
       <c r="Q5" s="255"/>
-    </row>
-    <row r="6" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R5" s="253" t="inlineStr">
+        <is>
+          <t>(Main rate %)</t>
+        </is>
+      </c>
+      <c r="S5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief fraction)</t>
+        </is>
+      </c>
+      <c r="T5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief lower limit)</t>
+        </is>
+      </c>
+      <c r="U5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief upper limit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="253"/>
       <c r="B6" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)-1</f>
@@ -16462,8 +16482,20 @@
       <c r="Q6" s="255" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R6" s="310">
+        <v>25</v>
+      </c>
+      <c r="S6" s="262">
+        <v>0.015</v>
+      </c>
+      <c r="T6" s="262">
+        <v>50000</v>
+      </c>
+      <c r="U6" s="262">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="253"/>
       <c r="B7" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)</f>
@@ -16505,6 +16537,18 @@
       </c>
       <c r="Q7" s="255" t="s">
         <v>268</v>
+      </c>
+      <c r="R7" s="310">
+        <v>25</v>
+      </c>
+      <c r="S7" s="262">
+        <v>0.015</v>
+      </c>
+      <c r="T7" s="262">
+        <v>50000</v>
+      </c>
+      <c r="U7" s="262">
+        <v>250000</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16526,23 +16570,15 @@
         <v>18</v>
       </c>
       <c r="H8" s="253"/>
-      <c r="I8" s="185" t="inlineStr">
-        <is>
-          <t>Corporation Tax main rate</t>
-        </is>
-      </c>
+      <c r="I8" s="185"/>
       <c r="J8" s="253"/>
       <c r="K8" s="253"/>
       <c r="L8" s="253"/>
       <c r="M8" s="253"/>
       <c r="N8" s="253"/>
       <c r="O8" s="253"/>
-      <c r="P8" s="310">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="255" t="s">
-        <v>268</v>
-      </c>
+      <c r="P8" s="310"/>
+      <c r="Q8" s="255"/>
     </row>
     <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="253"/>
@@ -16556,11 +16592,7 @@
       <c r="F9" s="253"/>
       <c r="G9" s="255"/>
       <c r="H9" s="253"/>
-      <c r="I9" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief fraction</t>
-        </is>
-      </c>
+      <c r="I9" s="185"/>
       <c r="J9" s="253"/>
       <c r="K9" s="253"/>
       <c r="L9" s="262" t="s">
@@ -16571,9 +16603,7 @@
         <v>521</v>
       </c>
       <c r="O9" s="263"/>
-      <c r="P9" s="262">
-        <v>0.015</v>
-      </c>
+      <c r="P9" s="262"/>
       <c r="Q9" s="255"/>
     </row>
     <row r="10" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16650,20 +16680,14 @@
       <c r="F12" s="253"/>
       <c r="G12" s="255"/>
       <c r="H12" s="253"/>
-      <c r="I12" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief lower limit</t>
-        </is>
-      </c>
+      <c r="I12" s="185"/>
       <c r="J12" s="253"/>
       <c r="K12" s="253"/>
       <c r="L12" s="253"/>
       <c r="M12" s="265"/>
       <c r="N12" s="255"/>
       <c r="O12" s="253"/>
-      <c r="P12" s="262">
-        <v>50000</v>
-      </c>
+      <c r="P12" s="262"/>
       <c r="Q12" s="255"/>
     </row>
     <row r="13" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16682,20 +16706,14 @@
         <v>268</v>
       </c>
       <c r="H13" s="253"/>
-      <c r="I13" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief upper limit</t>
-        </is>
-      </c>
+      <c r="I13" s="185"/>
       <c r="J13" s="253"/>
       <c r="K13" s="253"/>
       <c r="L13" s="253"/>
       <c r="M13" s="253"/>
       <c r="N13" s="253"/>
       <c r="O13" s="253"/>
-      <c r="P13" s="262">
-        <v>250000</v>
-      </c>
+      <c r="P13" s="262"/>
       <c r="Q13" s="253"/>
     </row>
     <row r="14" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -45013,7 +45031,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="441">
-        <f>IF(K30*A33/A35&lt;=Admin!$P$12*A33/A35/(1+Admin!$P$14),Admin!P6,Admin!$P$8)</f>
+        <f>IF(K30*A33/A35&lt;=Admin!$T$6*A33/A35/(1+Admin!$P$14),Admin!P6,Admin!$R$6)</f>
         <v>19</v>
       </c>
       <c r="H33" s="442"/>
@@ -45027,7 +45045,7 @@
       </c>
       <c r="K33" s="161"/>
       <c r="L33" s="38">
-        <f>IF(AND(K30*A33/A35&gt;Admin!$P$12*A33/A35/(1+Admin!$P$14),K30*A33/A35&lt;Admin!$P$13*A33/A35/(1+Admin!$P$14)),(Admin!$P$13*A33/A35/(1+Admin!$P$14)-K30*A33/A35)*F33/(K30*A33/A35)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A33/A35&gt;Admin!$T$6*A33/A35/(1+Admin!$P$14),K30*A33/A35&lt;Admin!$U$6*A33/A35/(1+Admin!$P$14)),(Admin!$U$6*A33/A35/(1+Admin!$P$14)-K30*A33/A35)*F33/(K30*A33/A35)*Admin!$S$6,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -45056,7 +45074,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="441">
-        <f>IF(K30*A34/A35&lt;=Admin!$P$12*A34/A35/(1+Admin!$P$14),Admin!P7,Admin!$P$8)</f>
+        <f>IF(K30*A34/A35&lt;=Admin!$T$7*A34/A35/(1+Admin!$P$14),Admin!P7,Admin!$R$7)</f>
         <v>19</v>
       </c>
       <c r="H34" s="442"/>
@@ -45070,7 +45088,7 @@
       </c>
       <c r="K34" s="161"/>
       <c r="L34" s="38">
-        <f>IF(AND(K30*A34/A35&gt;Admin!$P$12*A34/A35/(1+Admin!$P$14),K30*A34/A35&lt;Admin!$P$13*A34/A35/(1+Admin!$P$14)),(Admin!$P$13*A34/A35/(1+Admin!$P$14)-K30*A34/A35)*F34/(K30*A34/A35)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A34/A35&gt;Admin!$T$7*A34/A35/(1+Admin!$P$14),K30*A34/A35&lt;Admin!$U$7*A34/A35/(1+Admin!$P$14)),(Admin!$U$7*A34/A35/(1+Admin!$P$14)-K30*A34/A35)*F34/(K30*A34/A35)*Admin!$S$7,0)</f>
         <v>0</v>
       </c>
     </row>
